--- a/Excel/TEMPLATE ERSA.xlsx
+++ b/Excel/TEMPLATE ERSA.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\DANIEL\ANTIGRAVITY\PROJEK\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F926E678-1E57-4BD9-B016-C496AB5ABA77}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9F8BEF82-2AA6-415F-A12C-1511F2E53E6E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{9E3D796A-C8E5-4DAA-8D9D-D6D8DEEE2093}"/>
+    <workbookView xWindow="-24120" yWindow="-120" windowWidth="24240" windowHeight="13020" xr2:uid="{9E3D796A-C8E5-4DAA-8D9D-D6D8DEEE2093}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -1476,9 +1476,7 @@
       <c r="AH2" s="3" t="s">
         <v>142</v>
       </c>
-      <c r="AI2" s="3">
-        <v>200201</v>
-      </c>
+      <c r="AI2" s="3"/>
       <c r="AJ2" s="3" t="s">
         <v>143</v>
       </c>
@@ -1620,5 +1618,6 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="360" verticalDpi="360" r:id="rId1"/>
 </worksheet>
 </file>
--- a/Excel/TEMPLATE ERSA.xlsx
+++ b/Excel/TEMPLATE ERSA.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\DANIEL\ANTIGRAVITY\PROJEK\Excel\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\DANIEL\ANTIGRAVITY\MASTER DATA GOVERNANCE\MATERIAL MASTER\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F926E678-1E57-4BD9-B016-C496AB5ABA77}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{800603B1-21E0-4A1E-9E69-FEC1D5C5F4C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{9E3D796A-C8E5-4DAA-8D9D-D6D8DEEE2093}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="156" uniqueCount="153">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="168" uniqueCount="155">
   <si>
     <t>Material</t>
   </si>
@@ -435,21 +435,9 @@
     <t>F</t>
   </si>
   <si>
-    <t>ERSA</t>
-  </si>
-  <si>
-    <t>ESP030</t>
-  </si>
-  <si>
     <t>PC</t>
   </si>
   <si>
-    <t>Testing dari gmail</t>
-  </si>
-  <si>
-    <t>M6</t>
-  </si>
-  <si>
     <t>NORM</t>
   </si>
   <si>
@@ -465,40 +453,61 @@
     <t>X</t>
   </si>
   <si>
-    <t>SP01</t>
-  </si>
-  <si>
-    <t>V</t>
-  </si>
-  <si>
     <t>KG</t>
   </si>
   <si>
     <t>PD</t>
   </si>
   <si>
-    <t>ZWH6</t>
-  </si>
-  <si>
-    <t>RW9</t>
-  </si>
-  <si>
-    <t>PB</t>
-  </si>
-  <si>
     <t>M</t>
   </si>
   <si>
-    <t>C1</t>
-  </si>
-  <si>
     <t>KP</t>
+  </si>
+  <si>
+    <t>HALB</t>
+  </si>
+  <si>
+    <t>HSF005</t>
+  </si>
+  <si>
+    <t>M3</t>
+  </si>
+  <si>
+    <t>BENGKIRAI</t>
+  </si>
+  <si>
+    <t>18X26X339</t>
+  </si>
+  <si>
+    <t>SF01</t>
+  </si>
+  <si>
+    <t>S</t>
+  </si>
+  <si>
+    <t>ZGW1</t>
+  </si>
+  <si>
+    <t>PJ1</t>
+  </si>
+  <si>
+    <t>EX</t>
+  </si>
+  <si>
+    <t>E</t>
+  </si>
+  <si>
+    <t>TEST Upload QM (Not Used)</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="00000"/>
+  </numFmts>
   <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -548,14 +557,17 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -880,7 +892,7 @@
     <col min="4" max="4" width="14.1796875" style="2" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="15.453125" style="2" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="21.26953125" style="2" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="20.453125" style="2" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="22.453125" style="2" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="8.453125" style="2" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="23.6328125" style="2" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="18.08984375" style="2" bestFit="1" customWidth="1"/>
@@ -1407,62 +1419,52 @@
         <v>131</v>
       </c>
     </row>
-    <row r="2" spans="1:134" x14ac:dyDescent="0.3">
-      <c r="A2" s="3"/>
+    <row r="2" spans="1:134" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B2" s="3" t="s">
         <v>132</v>
       </c>
-      <c r="C2" s="3"/>
       <c r="D2" s="3" t="s">
+        <v>143</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="F2" s="3" t="s">
         <v>133</v>
       </c>
-      <c r="E2" s="3" t="s">
+      <c r="G2" s="3" t="s">
+        <v>154</v>
+      </c>
+      <c r="H2" s="3" t="s">
+        <v>145</v>
+      </c>
+      <c r="I2" s="3" t="s">
         <v>134</v>
       </c>
-      <c r="F2" s="3" t="s">
+      <c r="K2" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="L2" s="3">
+        <v>0</v>
+      </c>
+      <c r="M2" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="N2" s="3">
+        <v>1000</v>
+      </c>
+      <c r="T2" s="3" t="s">
         <v>135</v>
-      </c>
-      <c r="G2" s="3" t="s">
-        <v>136</v>
-      </c>
-      <c r="H2" s="3" t="s">
-        <v>137</v>
-      </c>
-      <c r="I2" s="3" t="s">
-        <v>138</v>
-      </c>
-      <c r="J2" s="3"/>
-      <c r="K2" s="3"/>
-      <c r="L2" s="3"/>
-      <c r="M2" s="3"/>
-      <c r="N2" s="3">
-        <v>1200</v>
-      </c>
-      <c r="O2" s="3">
-        <v>1207</v>
-      </c>
-      <c r="P2" s="3"/>
-      <c r="Q2" s="3"/>
-      <c r="R2" s="3"/>
-      <c r="S2" s="3"/>
-      <c r="T2" s="3" t="s">
-        <v>139</v>
       </c>
       <c r="U2" s="3">
         <v>1</v>
       </c>
       <c r="V2" s="3" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="W2" s="3" t="s">
-        <v>138</v>
-      </c>
-      <c r="X2" s="3"/>
-      <c r="Y2" s="3"/>
-      <c r="Z2" s="3"/>
-      <c r="AA2" s="3"/>
-      <c r="AB2" s="3"/>
-      <c r="AC2" s="3"/>
+        <v>134</v>
+      </c>
       <c r="AD2" s="3">
         <v>1</v>
       </c>
@@ -1470,29 +1472,28 @@
         <v>1</v>
       </c>
       <c r="AF2" s="3" t="s">
-        <v>141</v>
-      </c>
-      <c r="AG2" s="3"/>
+        <v>137</v>
+      </c>
       <c r="AH2" s="3" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="AI2" s="3">
-        <v>200201</v>
+        <v>100301</v>
       </c>
       <c r="AJ2" s="3" t="s">
-        <v>143</v>
+        <v>148</v>
       </c>
       <c r="AK2" s="3">
+        <v>1.58</v>
+      </c>
+      <c r="AL2" s="3">
         <v>0</v>
-      </c>
-      <c r="AL2" s="3">
-        <v>143.82</v>
       </c>
       <c r="AM2" s="3">
         <v>1</v>
       </c>
       <c r="AN2" s="3" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="AO2" s="3">
         <v>0</v>
@@ -1500,19 +1501,14 @@
       <c r="AP2" s="3">
         <v>0</v>
       </c>
-      <c r="AQ2" s="3"/>
       <c r="AR2" s="3">
         <v>0</v>
       </c>
-      <c r="AS2" s="3"/>
-      <c r="AT2" s="3"/>
-      <c r="AU2" s="3"/>
-      <c r="AV2" s="3"/>
       <c r="AW2" s="3">
         <v>0</v>
       </c>
       <c r="AX2" s="3" t="s">
-        <v>145</v>
+        <v>139</v>
       </c>
       <c r="AY2" s="3">
         <v>0</v>
@@ -1520,102 +1516,113 @@
       <c r="AZ2" s="3">
         <v>0</v>
       </c>
-      <c r="BA2" s="3"/>
-      <c r="BB2" s="3"/>
-      <c r="BC2" s="3"/>
-      <c r="BD2" s="3"/>
-      <c r="BE2" s="3"/>
-      <c r="BF2" s="3"/>
       <c r="BG2" s="3" t="s">
-        <v>146</v>
+        <v>140</v>
       </c>
       <c r="BH2" s="3" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="BI2" s="3" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="BJ2" s="3" t="s">
-        <v>149</v>
-      </c>
-      <c r="BK2" s="3"/>
-      <c r="BL2" s="3"/>
-      <c r="BM2" s="3"/>
+        <v>152</v>
+      </c>
       <c r="BN2" s="3" t="s">
-        <v>132</v>
-      </c>
-      <c r="BO2" s="3"/>
+        <v>153</v>
+      </c>
       <c r="BP2" s="3">
         <v>1</v>
       </c>
       <c r="BQ2" s="3">
         <v>0</v>
       </c>
-      <c r="BR2" s="3"/>
       <c r="BS2" s="3">
         <v>0</v>
       </c>
       <c r="BT2" s="3">
         <v>0</v>
       </c>
-      <c r="BU2" s="3"/>
-      <c r="BV2" s="3"/>
-      <c r="BW2" s="3"/>
-      <c r="BX2" s="3"/>
-      <c r="BY2" s="3"/>
+      <c r="BV2" s="3">
+        <v>20</v>
+      </c>
       <c r="BZ2" s="3" t="s">
-        <v>150</v>
-      </c>
-      <c r="CA2" s="3" t="s">
-        <v>151</v>
+        <v>141</v>
       </c>
       <c r="CB2" s="3" t="s">
-        <v>152</v>
-      </c>
-      <c r="CC2" s="3"/>
+        <v>142</v>
+      </c>
       <c r="CD2" s="3">
+        <v>1</v>
+      </c>
+      <c r="CF2" s="3">
+        <v>1307</v>
+      </c>
+      <c r="CH2" s="4">
         <v>2</v>
       </c>
-      <c r="CE2" s="3"/>
-      <c r="CF2" s="3"/>
-      <c r="CG2" s="3">
-        <v>1207</v>
-      </c>
-      <c r="CH2" s="3"/>
       <c r="CI2" s="3">
         <v>0</v>
       </c>
       <c r="CJ2" s="3">
         <v>0</v>
       </c>
-      <c r="CK2" s="3"/>
       <c r="CL2" s="3" t="s">
-        <v>142</v>
-      </c>
-      <c r="CM2" s="3"/>
+        <v>138</v>
+      </c>
+      <c r="CM2" s="3" t="s">
+        <v>138</v>
+      </c>
       <c r="CN2" s="3">
+        <v>100</v>
+      </c>
+      <c r="CQ2" s="4">
         <v>1</v>
       </c>
-      <c r="CO2" s="3"/>
-      <c r="CP2" s="3"/>
-      <c r="CQ2" s="3">
-        <v>1</v>
-      </c>
-      <c r="CR2" s="3"/>
-      <c r="CS2" s="3"/>
-      <c r="CT2" s="3"/>
-      <c r="CU2" s="3"/>
-      <c r="CV2" s="3"/>
-      <c r="CW2" s="3"/>
-      <c r="CX2" s="3"/>
-      <c r="CY2" s="3"/>
-      <c r="CZ2" s="3"/>
-      <c r="DA2" s="3"/>
-      <c r="DC2" s="2">
+      <c r="CR2" s="3">
+        <v>4</v>
+      </c>
+      <c r="CS2" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="CW2" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="CX2" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="CY2" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="CZ2" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="DA2" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="DC2" s="3">
         <v>0</v>
       </c>
-      <c r="DI2" s="2">
+      <c r="DE2" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="DF2" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="DH2" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="DI2" s="3">
         <v>0</v>
+      </c>
+      <c r="DK2" s="3">
+        <v>6</v>
+      </c>
+      <c r="DL2" s="3">
+        <v>6</v>
+      </c>
+      <c r="DO2" s="3" t="s">
+        <v>138</v>
       </c>
     </row>
   </sheetData>
